--- a/data/trans_camb/P1803_2016_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1803_2016_2023-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,93</t>
+          <t>-3,63; 5,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,1</t>
+          <t>-3,23; 4,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 3,19</t>
+          <t>-2,49; 3,81</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-7,56%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,31%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 134,68</t>
+          <t>-57,39; 133,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,42; 119,7</t>
+          <t>-55,21; 133,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 81,46</t>
+          <t>-41,37; 88,0</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>2,81</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 7,47</t>
+          <t>-0,3; 6,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,2</t>
+          <t>-0,45; 6,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,23</t>
+          <t>0,5; 5,48</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 215,63</t>
+          <t>-9,23; 206,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 118,81</t>
+          <t>-5,35; 126,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 125,12</t>
+          <t>6,94; 115,48</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>5,3</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,68</t>
+          <t>1,7; 8,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,28</t>
+          <t>2,98; 8,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,0</t>
+          <t>3,15; 7,41</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>116,05%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144,16%</t>
+          <t>121,81%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127,81%</t>
+          <t>100,88%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,87; 220,94</t>
+          <t>20,62; 180,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,69; 283,71</t>
+          <t>44,04; 242,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,03; 201,6</t>
+          <t>49,0; 172,22</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>30,58</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,38</t>
+          <t>5,84</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 67,36</t>
+          <t>2,41; 8,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,16</t>
+          <t>3,49; 8,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,9; 45,63</t>
+          <t>3,81; 7,73</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>637,92%</t>
+          <t>116,48%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104,32%</t>
+          <t>115,35%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>385,52%</t>
+          <t>116,1%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>92,51; 1811,31</t>
+          <t>36,93; 247,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,36; 213,46</t>
+          <t>48,32; 219,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88,55; 1102,28</t>
+          <t>63,32; 188,74</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>4,81</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,18</t>
+          <t>0,08; 5,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,98</t>
+          <t>3,0; 9,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,39</t>
+          <t>2,78; 7,02</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>110,59%</t>
+          <t>107,75%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,37; 189,56</t>
+          <t>-2,06; 179,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40,98; 213,7</t>
+          <t>33,29; 210,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41,42; 163,29</t>
+          <t>38,2; 162,44</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>4,08</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,03</t>
+          <t>1,88; 6,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 4,78</t>
+          <t>0,24; 7,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,96</t>
+          <t>1,78; 6,32</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>213,24%</t>
+          <t>211,04%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>43,93; 835,11</t>
+          <t>39,73; 656,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 80,89</t>
+          <t>1,72; 165,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 132,39</t>
+          <t>29,42; 186,42</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>1,98</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,93</t>
+          <t>-1,78; 3,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,11</t>
+          <t>0,05; 5,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,69</t>
+          <t>0,03; 3,89</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 204,48</t>
+          <t>-49,31; 221,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 236,8</t>
+          <t>-0,2; 247,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 166,55</t>
+          <t>-1,14; 184,5</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,48; 29,72</t>
+          <t>2,24; 4,72</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,25</t>
+          <t>3,26; 5,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,54; 18,48</t>
+          <t>3,07; 4,74</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>224,6%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>138,74%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>73,46; 708,35</t>
+          <t>44,5; 115,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>35,32; 104,21</t>
+          <t>54,76; 113,59</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>68,95; 388,12</t>
+          <t>55,54; 100,64</t>
         </is>
       </c>
     </row>
